--- a/Bronnenlijst PancakeScience.xlsx
+++ b/Bronnenlijst PancakeScience.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trist\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentkdg-my.sharepoint.com/personal/wouter_delaet_student_kdg_be/Documents/Level 3/Integratie_Pancake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6D5A0B-7730-439D-B939-9324982F64DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{FC6D5A0B-7730-439D-B939-9324982F64DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A81FF0B5-1575-46C5-BACB-33553BB8BDFC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>ArduinoJson Library - https://arduinojson.org/</t>
   </si>
@@ -182,6 +182,180 @@
   </si>
   <si>
     <t xml:space="preserve"> @Approute("/logs/csv")</t>
+  </si>
+  <si>
+    <t>Adafruit MLX90632 Guide - https://learn.adafruit.com/adafruit-mlx90632-fir-remote-thermal-temperature-sensor</t>
+  </si>
+  <si>
+    <t>I2C-registers correct instellen op 'Medical Mode' voor nauwkeurige metingen (niet standaard in Arduino docs).</t>
+  </si>
+  <si>
+    <t>.cpp Code: setup() &amp; loop(); Procesdoc: Fase 1, 4, 10</t>
+  </si>
+  <si>
+    <t>DFRobot RGB LCD1602 Wiki - https://wiki.dfrobot.com/Gravity__I2C_16x2_Arduino_LCD_with_RGB_Backlight_Display_SKU__DFR0464</t>
+  </si>
+  <si>
+    <t>Bevestiging van uniek I2C-adres (0x2D) en vereiste commando's voor achtergrondverlichting.</t>
+  </si>
+  <si>
+    <t>.cpp Code: Initialisatie &amp; setRGB(); Procesdoc: Fase 2, 5</t>
+  </si>
+  <si>
+    <t>AiP31068L Controller Datasheet - https://www.orientdisplay.com/wp-content/uploads/2022/08/AIP31068L.pdf</t>
+  </si>
+  <si>
+    <t>Correcte hex-code (0xDF) vinden in 'CGROM Mapping Table' omdat standaard ASCII niet werkte voor graden-teken.</t>
+  </si>
+  <si>
+    <t>.cpp Code: lcd.print((char)223); Procesdoc: Fase 2</t>
+  </si>
+  <si>
+    <t>Adafruit Rotary Encoder Specs - https://www.adafruit.com/product/377</t>
+  </si>
+  <si>
+    <t>Verificatie van incrementele encoder specificaties en interne drukknop werking.</t>
+  </si>
+  <si>
+    <t>.cpp Code: Input validatie loop; Procesdoc: Fase 3</t>
+  </si>
+  <si>
+    <t>Gravity Digital Relay Wiki - https://www.dfrobot.com/product-64.html</t>
+  </si>
+  <si>
+    <t>Verificatie schakellogica (Actief Hoog) voor veiligheid bij opstarten.</t>
+  </si>
+  <si>
+    <t>.cpp Code: digitalWrite(relayPin, HIGH); Procesdoc: Fase 1</t>
+  </si>
+  <si>
+    <t>Adafruit MLX90632 Library - https://github.com/adafruit/Adafruit_MLX90632</t>
+  </si>
+  <si>
+    <t>Officiële driver om I2C-communicatie te abstraheren naar functies zoals getTemperature().</t>
+  </si>
+  <si>
+    <t>DFRobot RGB LCD1602 Library - https://wiki.dfrobot.com/Gravity__I2C_16x2_Arduino_LCD_with_RGB_Backlight_Display_SKU__DFR0464</t>
+  </si>
+  <si>
+    <t>Essentiële driver voor aansturing RGB-kleuren via I2C.</t>
+  </si>
+  <si>
+    <t>Adafruit GFX Library - https://github.com/adafruit/Adafruit-GFX-Library</t>
+  </si>
+  <si>
+    <t>Industriestandaard voor graphics (fillRoundRect, tekst-rendering) op Arduino.</t>
+  </si>
+  <si>
+    <t>Adafruit ST7789 Library - https://github.com/adafruit/Adafruit-ST7735-Library</t>
+  </si>
+  <si>
+    <t>Hardware-specifieke driver om GFX-commando's te vertalen naar de ST7789 chip.</t>
+  </si>
+  <si>
+    <t>HowToMechatronics Rotary Encoder - https://howtomechatronics.com/tutorials/arduino/rotary-encoder-works-use-arduino/</t>
+  </si>
+  <si>
+    <t>Uitleg en algoritme voor "Quadrature Encoding" (fase-detectie) zonder zware library.</t>
+  </si>
+  <si>
+    <t>.cpp Code: Fase-detectie logica; Procesdoc: Fase 3</t>
+  </si>
+  <si>
+    <t>Arduino Docs Digital Pins - https://docs.arduino.cc/learn/microcontrollers/digital-pins/</t>
+  </si>
+  <si>
+    <t>Onderbouwing voor gebruik interne pull-up weerstanden (besparing componenten).</t>
+  </si>
+  <si>
+    <t>.cpp Code: pinMode(INPUT_PULLUP); Procesdoc: Fase 1, 3</t>
+  </si>
+  <si>
+    <t>Wikipedia Bang-Bang Control - https://en.wikipedia.org/wiki/Bang%E2%80%93bang_control</t>
+  </si>
+  <si>
+    <t>Theoretische validatie dat hysterese-regelaar stabiel is voor trage verwarming.</t>
+  </si>
+  <si>
+    <t>.cpp Code: Thermostaat logica; Procesdoc: Fase 4, 10</t>
+  </si>
+  <si>
+    <t>TutorialsPoint C Structures - https://www.tutorialspoint.com/cprogramming/c_structures.htm</t>
+  </si>
+  <si>
+    <t>Syntax naslagwerk om data-architectuur (Naam + Temp) schaalbaar op te zetten.</t>
+  </si>
+  <si>
+    <t>.cpp Code: struct Programma; Procesdoc: Fase 4</t>
+  </si>
+  <si>
+    <t>LearnCPP Forward Declarations - https://www.learncpp.com/cpp-tutorial/forward-declarations/</t>
+  </si>
+  <si>
+    <t>Oplossing voor compiler-fouten door functies bekend te maken voor definitie.</t>
+  </si>
+  <si>
+    <t>.cpp Code: Prototype void updateTFTMenu(); Procesdoc: Fase 5</t>
+  </si>
+  <si>
+    <t>Arduino Ref Arithmetic Operators - https://www.arduino.cc/reference/en/language/structure/arithmetic-operators/division/</t>
+  </si>
+  <si>
+    <t>Paginering-logica gebaseerd op integer truncation (afkappen decimalen).</t>
+  </si>
+  <si>
+    <t>.cpp Code: Paginering logica; Procesdoc: Fase 8</t>
+  </si>
+  <si>
+    <t>Arduino Ref SPI Protocol - https://docs.arduino.cc/language-reference/en/functions/communication/SPI/</t>
+  </si>
+  <si>
+    <t>Technische onderbouwing voor overstap van Software SPI naar Hardware SPI (snelheid).</t>
+  </si>
+  <si>
+    <t>.cpp Code: Constructor aanpassing; Procesdoc: Fase 5, 6</t>
+  </si>
+  <si>
+    <t>Adafruit GFX Primitives - https://learn.adafruit.com/adafruit-gfx-graphics-library/graphics-primitives</t>
+  </si>
+  <si>
+    <t>Oplossing flikkerend scherm door lokaal overschrijven (setTextColor met achtergrond).</t>
+  </si>
+  <si>
+    <t>.cpp Code: Anti-flikker logica; Procesdoc: Fase 6, 8, 10</t>
+  </si>
+  <si>
+    <t>Adafruit GFX RGB565 - https://learn.adafruit.com/adafruit-gfx-graphics-library/coordinate-system-and-units</t>
+  </si>
+  <si>
+    <t>Conversie van standaard hex-kleuren naar vereiste 16-bit formaat.</t>
+  </si>
+  <si>
+    <t>.cpp Code: Kleurdefinities; Procesdoc: Fase 5, 9</t>
+  </si>
+  <si>
+    <t>Google Gemini AI - https://gemini.google.com/</t>
+  </si>
+  <si>
+    <t>Co-Pilot voor complexe wiskunde (Sliding Window, Boundary Checks) en documentatie structuur.</t>
+  </si>
+  <si>
+    <t>13/12/2025 – 22/01/2026</t>
+  </si>
+  <si>
+    <t>.cpp Code: Sliding Window logica; Procesdoc: Fase 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (Sensor aansturing)</t>
+  </si>
+  <si>
+    <t>(LCD aansturing)</t>
+  </si>
+  <si>
+    <t>(Grafische vormen en tekst)</t>
+  </si>
+  <si>
+    <t>(Hardware Driver TFT)</t>
   </si>
 </sst>
 </file>
@@ -529,14 +703,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="97.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="115.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="96.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -828,6 +1002,329 @@
         <v>53</v>
       </c>
     </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="2">
+        <v>46009</v>
+      </c>
+      <c r="E19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2">
+        <v>46027</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="2">
+        <v>46029</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="2">
+        <v>46009</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="2">
+        <v>46009</v>
+      </c>
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46009</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46029</v>
+      </c>
+      <c r="E25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46034</v>
+      </c>
+      <c r="E26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="2">
+        <v>46034</v>
+      </c>
+      <c r="E27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="2">
+        <v>46028</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2">
+        <v>46007</v>
+      </c>
+      <c r="E29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="2">
+        <v>46027</v>
+      </c>
+      <c r="E30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="2">
+        <v>46034</v>
+      </c>
+      <c r="E31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45669</v>
+      </c>
+      <c r="E32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="2">
+        <v>46035</v>
+      </c>
+      <c r="E33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="2">
+        <v>46034</v>
+      </c>
+      <c r="E34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="2">
+        <v>46035</v>
+      </c>
+      <c r="E35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="2">
+        <v>46035</v>
+      </c>
+      <c r="E36" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
